--- a/hall/resources/sample/LoginRewards.xlsx
+++ b/hall/resources/sample/LoginRewards.xlsx
@@ -26,10 +26,46 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1. 每天签到
+2. 累积签到</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t>序列ID</t>
+  </si>
+  <si>
+    <t>类型</t>
   </si>
   <si>
     <t>签到天数</t>
@@ -41,10 +77,13 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}int&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{;}</t>
   </si>
   <si>
     <t>id</t>
+  </si>
+  <si>
+    <t>type</t>
   </si>
   <si>
     <t>days</t>
@@ -61,6 +100,9 @@
   <si>
     <t>1990000_10000;1980000_10000;1020001_99</t>
   </si>
+  <si>
+    <t>1990000_10000;1980000_10000</t>
+  </si>
 </sst>
 </file>
 
@@ -72,7 +114,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +277,17 @@
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="33">
@@ -687,7 +740,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -698,6 +751,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1039,15 +1095,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="2"/>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="2" width="9" style="1"/>
-    <col min="3" max="3" width="46" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="9" style="1"/>
+    <col min="4" max="4" width="46" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1057,108 +1113,209 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="C3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="1">
         <v>1</v>
       </c>
       <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1">
         <v>0</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="D4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="1">
         <v>2</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="C5" s="1">
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6" s="1">
         <v>3</v>
       </c>
       <c r="B6" s="1">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1">
         <v>2</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="D6" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7" s="1">
         <v>4</v>
       </c>
       <c r="B7" s="1">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1">
         <v>3</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="D7" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="1">
         <v>5</v>
       </c>
       <c r="B8" s="1">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1">
         <v>4</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="D8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="1">
         <v>6</v>
       </c>
       <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1">
         <v>5</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="D9" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="1">
         <v>7</v>
       </c>
       <c r="B10" s="1">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1">
         <v>6</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1">
+        <v>101</v>
+      </c>
+      <c r="B11" s="1">
+        <v>2</v>
+      </c>
+      <c r="C11" s="4">
+        <v>3</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1">
+        <v>102</v>
+      </c>
+      <c r="B12" s="1">
+        <v>2</v>
+      </c>
+      <c r="C12" s="4">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1">
+        <v>103</v>
+      </c>
+      <c r="B13" s="1">
+        <v>2</v>
+      </c>
+      <c r="C13" s="4">
+        <v>8</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1">
+        <v>104</v>
+      </c>
+      <c r="B14" s="1">
+        <v>2</v>
+      </c>
+      <c r="C14" s="4">
+        <v>15</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1">
+        <v>105</v>
+      </c>
+      <c r="B15" s="1">
+        <v>2</v>
+      </c>
+      <c r="C15" s="4">
+        <v>30</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/hall/resources/sample/LoginRewards.xlsx
+++ b/hall/resources/sample/LoginRewards.xlsx
@@ -279,12 +279,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -740,7 +740,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -751,6 +751,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -1095,7 +1098,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -1146,170 +1149,176 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="1">
-        <v>1</v>
-      </c>
-      <c r="B4" s="1">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1">
         <v>1</v>
       </c>
       <c r="C5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B6" s="1">
         <v>1</v>
       </c>
       <c r="C6" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="1">
         <v>1</v>
       </c>
       <c r="C7" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="1">
         <v>1</v>
       </c>
       <c r="C8" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
       </c>
       <c r="C9" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" s="1">
         <v>1</v>
       </c>
       <c r="C10" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1">
-        <v>101</v>
+        <v>7</v>
       </c>
       <c r="B11" s="1">
-        <v>2</v>
-      </c>
-      <c r="C11" s="4">
-        <v>3</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>10</v>
+        <v>1</v>
+      </c>
+      <c r="C11" s="1">
+        <v>6</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B12" s="1">
         <v>2</v>
       </c>
-      <c r="C12" s="4">
-        <v>5</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>11</v>
+      <c r="C12" s="5">
+        <v>3</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B13" s="1">
         <v>2</v>
       </c>
-      <c r="C13" s="4">
-        <v>8</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>10</v>
+      <c r="C13" s="5">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B14" s="1">
         <v>2</v>
       </c>
-      <c r="C14" s="4">
-        <v>15</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>13</v>
+      <c r="C14" s="5">
+        <v>8</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B15" s="1">
         <v>2</v>
       </c>
-      <c r="C15" s="4">
+      <c r="C15" s="5">
+        <v>15</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1">
+        <v>105</v>
+      </c>
+      <c r="B16" s="1">
+        <v>2</v>
+      </c>
+      <c r="C16" s="5">
         <v>30</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D16" s="1" t="s">
         <v>12</v>
       </c>
     </row>

--- a/hall/resources/sample/LoginRewards.xlsx
+++ b/hall/resources/sample/LoginRewards.xlsx
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
   <si>
     <t>序列ID</t>
   </si>
@@ -77,7 +77,7 @@
     <t>int</t>
   </si>
   <si>
-    <t>map&lt;int{_}long&gt;{;}</t>
+    <t>map&lt;int{_}long&gt;{|}</t>
   </si>
   <si>
     <t>id</t>
@@ -92,16 +92,40 @@
     <t>getItem</t>
   </si>
   <si>
-    <t>1990000_10000</t>
-  </si>
-  <si>
-    <t>1980000_10000</t>
-  </si>
-  <si>
-    <t>1990000_10000;1980000_10000;1020001_99</t>
-  </si>
-  <si>
-    <t>1990000_10000;1980000_10000</t>
+    <t>1990000_50000</t>
+  </si>
+  <si>
+    <t>1022501_2</t>
+  </si>
+  <si>
+    <t>1990000_100000</t>
+  </si>
+  <si>
+    <t>1980000_50</t>
+  </si>
+  <si>
+    <t>1990000_150000</t>
+  </si>
+  <si>
+    <t>1022502_2</t>
+  </si>
+  <si>
+    <t>1980000_100|1022503_2|1022501_2</t>
+  </si>
+  <si>
+    <t>1022501_4|1990000_150000</t>
+  </si>
+  <si>
+    <t>1022502_2|1990000_200000</t>
+  </si>
+  <si>
+    <t>1980000_100|1990000_275000</t>
+  </si>
+  <si>
+    <t>1022503_2|1990000_425000</t>
+  </si>
+  <si>
+    <t>1980000_300|1990000_575000</t>
   </si>
 </sst>
 </file>
@@ -1193,7 +1217,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1207,7 +1231,7 @@
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1221,7 +1245,7 @@
         <v>4</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1235,7 +1259,7 @@
         <v>5</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1249,7 +1273,7 @@
         <v>6</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1260,10 +1284,10 @@
         <v>2</v>
       </c>
       <c r="C12" s="5">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1274,10 +1298,10 @@
         <v>2</v>
       </c>
       <c r="C13" s="5">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1288,10 +1312,10 @@
         <v>2</v>
       </c>
       <c r="C14" s="5">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1302,10 +1326,10 @@
         <v>2</v>
       </c>
       <c r="C15" s="5">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1316,10 +1340,10 @@
         <v>2</v>
       </c>
       <c r="C16" s="5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
